--- a/code_mapping/[공통] 5. 관리항목매핑정의서.xlsx
+++ b/code_mapping/[공통] 5. 관리항목매핑정의서.xlsx
@@ -565,7 +565,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="325">
   <si>
     <t>SOURCE 회사코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1712,6 +1712,10 @@
 구분 = '9' : A08로 이관 ---신용카드(OmniEsol : 신용카드등록)
 그 외 구분 값 [전표입력]거래처에 이관되므로 관리항목이관 제외</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리항목매핑정의서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2381,7 +2385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2397,24 +2401,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2448,12 +2434,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2463,12 +2443,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2852,6 +2826,177 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3149,8 +3294,8 @@
       <sheetName val="관리항목(확인용)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
@@ -3431,303 +3576,332 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K21"/>
+  <dimension ref="B1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.125" customWidth="1"/>
-    <col min="2" max="11" width="30.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.125" style="176" customWidth="1"/>
+    <col min="2" max="3" width="30.625" style="193" customWidth="1"/>
+    <col min="4" max="6" width="30.625" style="194" customWidth="1"/>
+    <col min="7" max="8" width="30.625" style="193" customWidth="1"/>
+    <col min="9" max="10" width="30.625" style="194" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="193" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="176"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="135" t="s">
+    <row r="1" spans="2:11" s="55" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="164" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1" s="164">
+        <v>20260513</v>
+      </c>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="164"/>
+    </row>
+    <row r="2" spans="2:11" s="55" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="164"/>
+    </row>
+    <row r="3" spans="2:11" s="55" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="137"/>
-    </row>
-    <row r="3" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="138"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="140"/>
-    </row>
-    <row r="4" spans="2:11" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="29" t="s">
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
+      <c r="K3" s="150"/>
+    </row>
+    <row r="4" spans="2:11" s="55" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="151"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="152"/>
+      <c r="H4" s="152"/>
+      <c r="I4" s="152"/>
+      <c r="J4" s="152"/>
+      <c r="K4" s="153"/>
+    </row>
+    <row r="5" spans="2:11" s="55" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="165"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="165"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="165"/>
+    </row>
+    <row r="6" spans="2:11" s="55" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C6" s="155" t="s">
         <v>243</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D6" s="156" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E6" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F6" s="156" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G6" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H6" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I6" s="157" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J6" s="157" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K6" s="158" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="116.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="16" t="s">
+    <row r="7" spans="2:11" s="55" customFormat="1" ht="116.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C7" s="160" t="s">
         <v>243</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D7" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E7" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F7" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G7" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H7" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I7" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J7" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K7" s="163" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="15"/>
-    </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="11"/>
+      <c r="B8" s="168"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="170"/>
+      <c r="F8" s="171"/>
+      <c r="G8" s="172"/>
+      <c r="H8" s="173"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="174"/>
+      <c r="K8" s="175"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="5"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="9"/>
+      <c r="B9" s="177"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="179"/>
+      <c r="E9" s="179"/>
+      <c r="F9" s="180"/>
+      <c r="G9" s="181"/>
+      <c r="H9" s="182"/>
+      <c r="I9" s="183"/>
+      <c r="J9" s="183"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="9"/>
+      <c r="B10" s="177"/>
+      <c r="C10" s="178"/>
+      <c r="D10" s="179"/>
+      <c r="E10" s="179"/>
+      <c r="F10" s="180"/>
+      <c r="G10" s="181"/>
+      <c r="H10" s="182"/>
+      <c r="I10" s="183"/>
+      <c r="J10" s="183"/>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="5"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="9"/>
+      <c r="B11" s="177"/>
+      <c r="C11" s="178"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="179"/>
+      <c r="F11" s="180"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="183"/>
+      <c r="J11" s="183"/>
+      <c r="K11" s="184"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="5"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="9"/>
+      <c r="B12" s="177"/>
+      <c r="C12" s="178"/>
+      <c r="D12" s="179"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="180"/>
+      <c r="G12" s="181"/>
+      <c r="H12" s="182"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="183"/>
+      <c r="K12" s="184"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="5"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="9"/>
+      <c r="B13" s="177"/>
+      <c r="C13" s="178"/>
+      <c r="D13" s="179"/>
+      <c r="E13" s="179"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="182"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="183"/>
+      <c r="K13" s="184"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="5"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="9"/>
+      <c r="B14" s="177"/>
+      <c r="C14" s="178"/>
+      <c r="D14" s="179"/>
+      <c r="E14" s="179"/>
+      <c r="F14" s="180"/>
+      <c r="G14" s="181"/>
+      <c r="H14" s="182"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="183"/>
+      <c r="K14" s="184"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="5"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="9"/>
+      <c r="B15" s="177"/>
+      <c r="C15" s="178"/>
+      <c r="D15" s="179"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="180"/>
+      <c r="G15" s="181"/>
+      <c r="H15" s="182"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="184"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="9"/>
+      <c r="B16" s="177"/>
+      <c r="C16" s="178"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="180"/>
+      <c r="G16" s="181"/>
+      <c r="H16" s="182"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="183"/>
+      <c r="K16" s="184"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="5"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="9"/>
+      <c r="B17" s="177"/>
+      <c r="C17" s="178"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="179"/>
+      <c r="F17" s="180"/>
+      <c r="G17" s="181"/>
+      <c r="H17" s="182"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="183"/>
+      <c r="K17" s="184"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="5"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="9"/>
+      <c r="B18" s="177"/>
+      <c r="C18" s="178"/>
+      <c r="D18" s="179"/>
+      <c r="E18" s="179"/>
+      <c r="F18" s="180"/>
+      <c r="G18" s="181"/>
+      <c r="H18" s="182"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="183"/>
+      <c r="K18" s="184"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="5"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="9"/>
+      <c r="B19" s="177"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="179"/>
+      <c r="F19" s="180"/>
+      <c r="G19" s="181"/>
+      <c r="H19" s="182"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="183"/>
+      <c r="K19" s="184"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="5"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="10"/>
+      <c r="B20" s="177"/>
+      <c r="C20" s="178"/>
+      <c r="D20" s="179"/>
+      <c r="E20" s="179"/>
+      <c r="F20" s="180"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="182"/>
+      <c r="I20" s="183"/>
+      <c r="J20" s="183"/>
+      <c r="K20" s="184"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="177"/>
+      <c r="C21" s="178"/>
+      <c r="D21" s="179"/>
+      <c r="E21" s="179"/>
+      <c r="F21" s="180"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="182"/>
+      <c r="I21" s="183"/>
+      <c r="J21" s="183"/>
+      <c r="K21" s="184"/>
+    </row>
+    <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="185"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="187"/>
+      <c r="E22" s="187"/>
+      <c r="F22" s="188"/>
+      <c r="G22" s="189"/>
+      <c r="H22" s="190"/>
+      <c r="I22" s="191"/>
+      <c r="J22" s="191"/>
+      <c r="K22" s="192"/>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
-    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="B3:K4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3745,36 +3919,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="125" t="s">
         <v>313</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="137"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="127"/>
     </row>
     <row r="3" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="138"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="140"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="130"/>
     </row>
     <row r="4" spans="2:11" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
@@ -3788,674 +3962,675 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="21" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="116.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="104" t="s">
         <v>244</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="105" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115"/>
-      <c r="F7" s="116">
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="106">
         <v>1000</v>
       </c>
-      <c r="G7" s="116" t="s">
+      <c r="G7" s="106" t="s">
         <v>290</v>
       </c>
-      <c r="H7" s="117" t="s">
+      <c r="H7" s="107" t="s">
         <v>245</v>
       </c>
-      <c r="I7" s="132" t="s">
+      <c r="I7" s="122" t="s">
         <v>317</v>
       </c>
-      <c r="J7" s="132" t="s">
+      <c r="J7" s="122" t="s">
         <v>315</v>
       </c>
-      <c r="K7" s="118" t="s">
+      <c r="K7" s="108" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="14">
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="8">
         <v>1000</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="I8" s="133" t="s">
+      <c r="I8" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="J8" s="133" t="s">
+      <c r="J8" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="9" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="14">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="8">
         <v>1000</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="I9" s="133" t="s">
+      <c r="I9" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="J9" s="133" t="s">
+      <c r="J9" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="9" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="14">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="8">
         <v>1000</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="I10" s="133" t="s">
+      <c r="I10" s="123" t="s">
         <v>320</v>
       </c>
-      <c r="J10" s="133" t="s">
+      <c r="J10" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="15"/>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="14">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="8">
         <v>1000</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="I11" s="133" t="s">
+      <c r="I11" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="133" t="s">
+      <c r="J11" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="15"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="14">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="8">
         <v>1000</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="I12" s="133" t="s">
+      <c r="I12" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="133" t="s">
+      <c r="J12" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="14">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="8">
         <v>1000</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="I13" s="133" t="s">
+      <c r="I13" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="133" t="s">
+      <c r="J13" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="14">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="8">
         <v>1000</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="I14" s="133" t="s">
+      <c r="I14" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="133" t="s">
+      <c r="J14" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="15"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="14">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="8">
         <v>1000</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="I15" s="133" t="s">
+      <c r="I15" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="133" t="s">
+      <c r="J15" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="15"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="14">
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="8">
         <v>1000</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="I16" s="133" t="s">
+      <c r="I16" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J16" s="133" t="s">
+      <c r="J16" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="9"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="14">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="8">
         <v>1000</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="I17" s="133" t="s">
+      <c r="I17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="133" t="s">
+      <c r="J17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="14">
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="8">
         <v>1000</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="I18" s="133" t="s">
+      <c r="I18" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="133" t="s">
+      <c r="J18" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K18" s="15"/>
+      <c r="K18" s="9"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="1">
         <v>1000</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="I19" s="133" t="s">
+      <c r="I19" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="133" t="s">
+      <c r="J19" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="11"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="1">
         <v>1000</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="I20" s="133" t="s">
+      <c r="I20" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="133" t="s">
+      <c r="J20" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="11"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="1">
         <v>1000</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="I21" s="133" t="s">
+      <c r="I21" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="133" t="s">
+      <c r="J21" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="11"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="1">
         <v>1000</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="H22" s="21" t="s">
+      <c r="H22" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="I22" s="133" t="s">
+      <c r="I22" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="133" t="s">
+      <c r="J22" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="11"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="1">
         <v>1000</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="I23" s="133" t="s">
+      <c r="I23" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="133" t="s">
+      <c r="J23" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K23" s="11"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="1">
         <v>1000</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="I24" s="133" t="s">
+      <c r="I24" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="133" t="s">
+      <c r="J24" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K24" s="11"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="1">
         <v>1000</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H25" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="I25" s="133" t="s">
+      <c r="I25" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="133" t="s">
+      <c r="J25" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="11"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="1">
         <v>1000</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="I26" s="133" t="s">
+      <c r="I26" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J26" s="133" t="s">
+      <c r="J26" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="11"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
       <c r="F27" s="1">
         <v>1000</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="I27" s="133" t="s">
+      <c r="I27" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J27" s="133" t="s">
+      <c r="J27" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K27" s="11"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
       <c r="F28" s="1">
         <v>1000</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H28" s="21" t="s">
+      <c r="H28" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="I28" s="133" t="s">
+      <c r="I28" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="133" t="s">
+      <c r="J28" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="11"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="119" t="s">
+      <c r="B29" s="109" t="s">
         <v>288</v>
       </c>
-      <c r="C29" s="120" t="s">
+      <c r="C29" s="110" t="s">
         <v>289</v>
       </c>
-      <c r="D29" s="120"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="121">
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="111">
         <v>1000</v>
       </c>
-      <c r="G29" s="121" t="s">
+      <c r="G29" s="111" t="s">
         <v>312</v>
       </c>
-      <c r="H29" s="122" t="s">
+      <c r="H29" s="112" t="s">
         <v>289</v>
       </c>
-      <c r="I29" s="134" t="s">
+      <c r="I29" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="134" t="s">
+      <c r="J29" s="124" t="s">
         <v>316</v>
       </c>
-      <c r="K29" s="123"/>
+      <c r="K29" s="113"/>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:K3"/>
   </mergeCells>
@@ -4472,44 +4647,44 @@
   <cols>
     <col min="1" max="1" width="2.125" customWidth="1"/>
     <col min="2" max="7" width="30.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="30.625" style="41" customWidth="1"/>
+    <col min="8" max="8" width="30.625" style="31" customWidth="1"/>
     <col min="9" max="10" width="30.625" style="3" customWidth="1"/>
     <col min="11" max="11" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
       <c r="H1" s="3"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="125" t="s">
         <v>314</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="137"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="127"/>
     </row>
     <row r="3" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="138"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="140"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="130"/>
     </row>
     <row r="4" spans="2:12" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
@@ -4523,1437 +4698,1438 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="21" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="116.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="124" t="s">
+      <c r="B7" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="C7" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="36" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="J7" s="39" t="s">
+      <c r="J7" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="L7" s="41"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="116" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="127" t="s">
+      <c r="C8" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="42"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="44" t="s">
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="45" t="s">
+      <c r="I8" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="J8" s="47" t="s">
+      <c r="J8" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="K8" s="48" t="s">
+      <c r="K8" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="L8" s="41"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="126" t="s">
+      <c r="B9" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="127" t="s">
+      <c r="C9" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="44" t="s">
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="46" t="s">
+      <c r="H9" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="I9" s="45" t="s">
+      <c r="I9" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="47" t="s">
+      <c r="J9" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="48" t="s">
+      <c r="K9" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="L9" s="41"/>
+      <c r="L9" s="31"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="126" t="s">
+      <c r="B10" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="127" t="s">
+      <c r="C10" s="117" t="s">
         <v>197</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="44" t="s">
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="46" t="s">
+      <c r="H10" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="I10" s="45" t="s">
+      <c r="I10" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="47" t="s">
+      <c r="J10" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="126" t="s">
+      <c r="B11" s="116" t="s">
         <v>225</v>
       </c>
-      <c r="C11" s="127" t="s">
+      <c r="C11" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="44" t="s">
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="46" t="s">
+      <c r="H11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="45" t="s">
+      <c r="I11" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="47" t="s">
+      <c r="J11" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="41"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="31"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="120" t="s">
         <v>226</v>
       </c>
-      <c r="C12" s="131" t="s">
+      <c r="C12" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="40">
         <v>0</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G12" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="51" t="s">
+      <c r="I12" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="47" t="s">
+      <c r="J12" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="41"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="31"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="120" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="131" t="s">
+      <c r="C13" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="40">
         <v>0</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="51" t="s">
+      <c r="G13" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="49" t="s">
+      <c r="H13" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="51" t="s">
+      <c r="I13" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="47" t="s">
+      <c r="J13" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="41"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="31"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="130" t="s">
+      <c r="B14" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="C14" s="131" t="s">
+      <c r="C14" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="40">
         <v>0</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="51" t="s">
+      <c r="G14" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="51" t="s">
+      <c r="I14" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="47" t="s">
+      <c r="J14" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="41"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="31"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="130" t="s">
+      <c r="B15" s="120" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="131" t="s">
+      <c r="C15" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="40">
         <v>0</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="51" t="s">
+      <c r="G15" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="51" t="s">
+      <c r="I15" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="47" t="s">
+      <c r="J15" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="41"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="31"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="126" t="s">
+      <c r="B16" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="127" t="s">
+      <c r="C16" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="44" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="51" t="s">
+      <c r="G16" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="51" t="s">
+      <c r="I16" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="47" t="s">
+      <c r="J16" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="41"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="31"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="126" t="s">
+      <c r="B17" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="127" t="s">
+      <c r="C17" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="44" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="51" t="s">
+      <c r="G17" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="49" t="s">
+      <c r="H17" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="I17" s="51" t="s">
+      <c r="I17" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="47" t="s">
+      <c r="J17" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="41"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="31"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="116" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="127" t="s">
+      <c r="C18" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="44" t="s">
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="51" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="49" t="s">
+      <c r="H18" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="51" t="s">
+      <c r="I18" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="47" t="s">
+      <c r="J18" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="41"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="112" t="s">
+      <c r="C19" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="44" t="s">
+      <c r="E19" s="40"/>
+      <c r="F19" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="51" t="s">
+      <c r="G19" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="49" t="s">
+      <c r="H19" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="51" t="s">
+      <c r="I19" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="47" t="s">
+      <c r="J19" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="41"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="31"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="111" t="s">
+      <c r="C20" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="44" t="s">
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="51" t="s">
+      <c r="G20" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="49" t="s">
+      <c r="H20" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="I20" s="51" t="s">
+      <c r="I20" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J20" s="47" t="s">
+      <c r="J20" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="41"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="31"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="126" t="s">
+      <c r="B21" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="127" t="s">
+      <c r="C21" s="117" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="44" t="s">
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="51" t="s">
+      <c r="G21" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="H21" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="I21" s="51" t="s">
+      <c r="I21" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="47" t="s">
+      <c r="J21" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="41"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="31"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="126" t="s">
+      <c r="B22" s="116" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="127" t="s">
+      <c r="C22" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="44" t="s">
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="51" t="s">
+      <c r="G22" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="49" t="s">
+      <c r="H22" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="I22" s="51" t="s">
+      <c r="I22" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J22" s="47" t="s">
+      <c r="J22" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="41"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="31"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="128" t="s">
+      <c r="B23" s="118" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="129" t="s">
+      <c r="C23" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="44" t="s">
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="51" t="s">
+      <c r="G23" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="H23" s="49" t="s">
+      <c r="H23" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="I23" s="51" t="s">
+      <c r="I23" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="47" t="s">
+      <c r="J23" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="41"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="31"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="128" t="s">
+      <c r="B24" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="129" t="s">
+      <c r="C24" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="44" t="s">
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="51" t="s">
+      <c r="G24" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="H24" s="49" t="s">
+      <c r="H24" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="I24" s="51" t="s">
+      <c r="I24" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="47" t="s">
+      <c r="J24" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="41"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="31"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="126" t="s">
+      <c r="B25" s="116" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="127" t="s">
+      <c r="C25" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="44" t="s">
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="51" t="s">
+      <c r="G25" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="H25" s="49" t="s">
+      <c r="H25" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="47" t="s">
+      <c r="J25" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="41"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="31"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="126" t="s">
+      <c r="B26" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="127" t="s">
+      <c r="C26" s="117" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="44" t="s">
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="51" t="s">
+      <c r="G26" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J26" s="47" t="s">
+      <c r="J26" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K26" s="56"/>
+      <c r="K26" s="46"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="127" t="s">
+      <c r="C27" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="44" t="s">
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G27" s="51" t="s">
+      <c r="G27" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="H27" s="49" t="s">
+      <c r="H27" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="51" t="s">
+      <c r="I27" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="47" t="s">
+      <c r="J27" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K27" s="56"/>
+      <c r="K27" s="46"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="111" t="s">
+      <c r="C28" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="50" t="s">
+      <c r="D28" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="40">
         <v>0</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F28" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G28" s="51" t="s">
+      <c r="G28" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="H28" s="49" t="s">
+      <c r="H28" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="47" t="s">
+      <c r="J28" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K28" s="56"/>
+      <c r="K28" s="46"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B29" s="126" t="s">
+      <c r="B29" s="116" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="127" t="s">
+      <c r="C29" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="44" t="s">
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G29" s="51" t="s">
+      <c r="G29" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="H29" s="49" t="s">
+      <c r="H29" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="I29" s="51" t="s">
+      <c r="I29" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="47" t="s">
+      <c r="J29" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="56"/>
+      <c r="K29" s="46"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B30" s="126" t="s">
+      <c r="B30" s="116" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="127" t="s">
+      <c r="C30" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="44" t="s">
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G30" s="51" t="s">
+      <c r="G30" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="H30" s="49" t="s">
+      <c r="H30" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="51" t="s">
+      <c r="I30" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J30" s="47" t="s">
+      <c r="J30" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K30" s="56"/>
+      <c r="K30" s="46"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B31" s="126" t="s">
+      <c r="B31" s="116" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="127" t="s">
+      <c r="C31" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="44" t="s">
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G31" s="51" t="s">
+      <c r="G31" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="H31" s="49" t="s">
+      <c r="H31" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="I31" s="51" t="s">
+      <c r="I31" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J31" s="47" t="s">
+      <c r="J31" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K31" s="56"/>
+      <c r="K31" s="46"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="126" t="s">
+      <c r="B32" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="127" t="s">
+      <c r="C32" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="44" t="s">
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G32" s="51" t="s">
+      <c r="G32" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="H32" s="49" t="s">
+      <c r="H32" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="I32" s="51" t="s">
+      <c r="I32" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J32" s="47" t="s">
+      <c r="J32" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="56"/>
+      <c r="K32" s="46"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="126" t="s">
+      <c r="B33" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="127" t="s">
+      <c r="C33" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="44" t="s">
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G33" s="51" t="s">
+      <c r="G33" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="H33" s="49" t="s">
+      <c r="H33" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="I33" s="51" t="s">
+      <c r="I33" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J33" s="47" t="s">
+      <c r="J33" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K33" s="56"/>
+      <c r="K33" s="46"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="126" t="s">
+      <c r="B34" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="127" t="s">
+      <c r="C34" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="44" t="s">
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G34" s="51" t="s">
+      <c r="G34" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="H34" s="49" t="s">
+      <c r="H34" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="I34" s="51" t="s">
+      <c r="I34" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J34" s="47" t="s">
+      <c r="J34" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K34" s="56"/>
+      <c r="K34" s="46"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="126" t="s">
+      <c r="B35" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="127" t="s">
+      <c r="C35" s="117" t="s">
         <v>101</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="44" t="s">
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="51" t="s">
+      <c r="G35" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="H35" s="49" t="s">
+      <c r="H35" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="I35" s="51" t="s">
+      <c r="I35" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J35" s="47" t="s">
+      <c r="J35" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K35" s="56"/>
+      <c r="K35" s="46"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B36" s="52" t="s">
+      <c r="B36" s="42" t="s">
         <v>232</v>
       </c>
-      <c r="C36" s="111" t="s">
+      <c r="C36" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="50" t="s">
+      <c r="D36" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="40">
         <v>3</v>
       </c>
-      <c r="F36" s="44" t="s">
+      <c r="F36" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="50" t="s">
+      <c r="G36" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="53" t="s">
+      <c r="H36" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="I36" s="50" t="s">
+      <c r="I36" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="47" t="s">
+      <c r="J36" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K36" s="56"/>
+      <c r="K36" s="46"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B37" s="52" t="s">
+      <c r="B37" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="C37" s="111" t="s">
+      <c r="C37" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="50" t="s">
+      <c r="D37" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="50">
+      <c r="E37" s="40">
         <v>2</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F37" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G37" s="51" t="s">
+      <c r="G37" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="H37" s="49" t="s">
+      <c r="H37" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="I37" s="51" t="s">
+      <c r="I37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J37" s="47" t="s">
+      <c r="J37" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K37" s="56"/>
+      <c r="K37" s="46"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B38" s="126" t="s">
+      <c r="B38" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="127" t="s">
+      <c r="C38" s="117" t="s">
         <v>108</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="44" t="s">
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G38" s="50" t="s">
+      <c r="G38" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="H38" s="53" t="s">
+      <c r="H38" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="I38" s="50" t="s">
+      <c r="I38" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="J38" s="47" t="s">
+      <c r="J38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K38" s="56"/>
+      <c r="K38" s="46"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B39" s="52" t="s">
+      <c r="B39" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="C39" s="111" t="s">
+      <c r="C39" s="101" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="50" t="s">
+      <c r="D39" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="50">
+      <c r="E39" s="40">
         <v>2</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G39" s="50" t="s">
+      <c r="G39" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="H39" s="53" t="s">
+      <c r="H39" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="I39" s="50" t="s">
+      <c r="I39" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="J39" s="47" t="s">
+      <c r="J39" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K39" s="56"/>
+      <c r="K39" s="46"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="111" t="s">
+      <c r="C40" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="44" t="s">
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="50" t="s">
+      <c r="G40" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="H40" s="53" t="s">
+      <c r="H40" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="I40" s="50" t="s">
+      <c r="I40" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="J40" s="47" t="s">
+      <c r="J40" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K40" s="56"/>
+      <c r="K40" s="46"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="126" t="s">
+      <c r="B41" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="C41" s="127" t="s">
+      <c r="C41" s="117" t="s">
         <v>116</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="44" t="s">
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="51" t="s">
+      <c r="G41" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="H41" s="49" t="s">
+      <c r="H41" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="I41" s="51" t="s">
+      <c r="I41" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J41" s="47" t="s">
+      <c r="J41" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K41" s="56"/>
+      <c r="K41" s="46"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B42" s="52" t="s">
+      <c r="B42" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="111" t="s">
+      <c r="C42" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="44" t="s">
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G42" s="51" t="s">
+      <c r="G42" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="H42" s="49" t="s">
+      <c r="H42" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="I42" s="51" t="s">
+      <c r="I42" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J42" s="47" t="s">
+      <c r="J42" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K42" s="56"/>
+      <c r="K42" s="46"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="126" t="s">
+      <c r="B43" s="116" t="s">
         <v>122</v>
       </c>
-      <c r="C43" s="127" t="s">
+      <c r="C43" s="117" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="44" t="s">
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G43" s="51" t="s">
+      <c r="G43" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="H43" s="49" t="s">
+      <c r="H43" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="51" t="s">
+      <c r="I43" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J43" s="47" t="s">
+      <c r="J43" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K43" s="56"/>
+      <c r="K43" s="46"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="52" t="s">
+      <c r="B44" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="111" t="s">
+      <c r="C44" s="101" t="s">
         <v>126</v>
       </c>
-      <c r="D44" s="50" t="s">
+      <c r="D44" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="50">
+      <c r="E44" s="40">
         <v>2</v>
       </c>
-      <c r="F44" s="44" t="s">
+      <c r="F44" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G44" s="51" t="s">
+      <c r="G44" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="H44" s="49" t="s">
+      <c r="H44" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="I44" s="51" t="s">
+      <c r="I44" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J44" s="47" t="s">
+      <c r="J44" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="56"/>
+      <c r="K44" s="46"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B45" s="52" t="s">
+      <c r="B45" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="111" t="s">
+      <c r="C45" s="101" t="s">
         <v>129</v>
       </c>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="44" t="s">
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G45" s="50" t="s">
+      <c r="G45" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="H45" s="53" t="s">
+      <c r="H45" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="I45" s="50" t="s">
+      <c r="I45" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="J45" s="47" t="s">
+      <c r="J45" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K45" s="56"/>
+      <c r="K45" s="46"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="126" t="s">
+      <c r="B46" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="127" t="s">
+      <c r="C46" s="117" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="44" t="s">
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G46" s="51" t="s">
+      <c r="G46" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="H46" s="49" t="s">
+      <c r="H46" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="I46" s="51" t="s">
+      <c r="I46" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J46" s="47" t="s">
+      <c r="J46" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K46" s="56"/>
+      <c r="K46" s="46"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="52" t="s">
+      <c r="B47" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="111" t="s">
+      <c r="C47" s="101" t="s">
         <v>135</v>
       </c>
-      <c r="D47" s="50" t="s">
+      <c r="D47" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E47" s="50">
+      <c r="E47" s="40">
         <v>4</v>
       </c>
-      <c r="F47" s="44" t="s">
+      <c r="F47" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G47" s="51" t="s">
+      <c r="G47" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="H47" s="49" t="s">
+      <c r="H47" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="I47" s="51" t="s">
+      <c r="I47" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J47" s="47" t="s">
+      <c r="J47" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K47" s="56"/>
+      <c r="K47" s="46"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="116" t="s">
         <v>137</v>
       </c>
-      <c r="C48" s="127" t="s">
+      <c r="C48" s="117" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="44" t="s">
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G48" s="51" t="s">
+      <c r="G48" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="H48" s="49" t="s">
+      <c r="H48" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="I48" s="51" t="s">
+      <c r="I48" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J48" s="47" t="s">
+      <c r="J48" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K48" s="56"/>
+      <c r="K48" s="46"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49" s="126" t="s">
+      <c r="B49" s="116" t="s">
         <v>140</v>
       </c>
-      <c r="C49" s="127" t="s">
+      <c r="C49" s="117" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="50"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="44" t="s">
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G49" s="51" t="s">
+      <c r="G49" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="H49" s="49" t="s">
+      <c r="H49" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="I49" s="51" t="s">
+      <c r="I49" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="47" t="s">
+      <c r="J49" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K49" s="56"/>
+      <c r="K49" s="46"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="126" t="s">
+      <c r="B50" s="116" t="s">
         <v>143</v>
       </c>
-      <c r="C50" s="127" t="s">
+      <c r="C50" s="117" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="50"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="44" t="s">
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G50" s="51" t="s">
+      <c r="G50" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="H50" s="49" t="s">
+      <c r="H50" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="I50" s="51" t="s">
+      <c r="I50" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="47" t="s">
+      <c r="J50" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K50" s="56"/>
+      <c r="K50" s="46"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="126" t="s">
+      <c r="B51" s="116" t="s">
         <v>147</v>
       </c>
-      <c r="C51" s="127" t="s">
+      <c r="C51" s="117" t="s">
         <v>148</v>
       </c>
-      <c r="D51" s="50"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="44" t="s">
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G51" s="51" t="s">
+      <c r="G51" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="H51" s="49" t="s">
+      <c r="H51" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="I51" s="51" t="s">
+      <c r="I51" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J51" s="47" t="s">
+      <c r="J51" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K51" s="56"/>
+      <c r="K51" s="46"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B52" s="126" t="s">
+      <c r="B52" s="116" t="s">
         <v>151</v>
       </c>
-      <c r="C52" s="127" t="s">
+      <c r="C52" s="117" t="s">
         <v>152</v>
       </c>
-      <c r="D52" s="50"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="44" t="s">
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G52" s="51" t="s">
+      <c r="G52" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="H52" s="49" t="s">
+      <c r="H52" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="I52" s="51" t="s">
+      <c r="I52" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J52" s="47" t="s">
+      <c r="J52" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K52" s="56"/>
+      <c r="K52" s="46"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B53" s="54" t="s">
+      <c r="B53" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="C53" s="112" t="s">
+      <c r="C53" s="102" t="s">
         <v>155</v>
       </c>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="44" t="s">
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="G53" s="57" t="s">
+      <c r="G53" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="H53" s="55" t="s">
+      <c r="H53" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="I53" s="51" t="s">
+      <c r="I53" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J53" s="47" t="s">
+      <c r="J53" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="K53" s="56"/>
+      <c r="K53" s="46"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B54" s="54" t="s">
+      <c r="B54" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="C54" s="112" t="s">
+      <c r="C54" s="102" t="s">
         <v>157</v>
       </c>
-      <c r="D54" s="57"/>
-      <c r="E54" s="57"/>
-      <c r="F54" s="44" t="s">
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G54" s="57" t="s">
+      <c r="G54" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="H54" s="55" t="s">
+      <c r="H54" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="I54" s="51" t="s">
+      <c r="I54" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J54" s="47" t="s">
+      <c r="J54" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K54" s="56"/>
+      <c r="K54" s="46"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="C55" s="112" t="s">
+      <c r="C55" s="102" t="s">
         <v>159</v>
       </c>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="44" t="s">
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="G55" s="57" t="s">
+      <c r="G55" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="H55" s="55" t="s">
+      <c r="H55" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="I55" s="51" t="s">
+      <c r="I55" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="J55" s="47" t="s">
+      <c r="J55" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K55" s="56"/>
+      <c r="K55" s="46"/>
     </row>
     <row r="56" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="58" t="s">
+      <c r="B56" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="C56" s="113" t="s">
+      <c r="C56" s="103" t="s">
         <v>161</v>
       </c>
-      <c r="D56" s="60"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="61" t="s">
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G56" s="60" t="s">
+      <c r="G56" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="H56" s="59" t="s">
+      <c r="H56" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="I56" s="60" t="s">
+      <c r="I56" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="J56" s="62" t="s">
+      <c r="J56" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="K56" s="63"/>
+      <c r="K56" s="53"/>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:K3"/>
   </mergeCells>
@@ -5983,1391 +6159,1392 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
-    <col min="2" max="2" width="4.375" style="32" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="64" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="65" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="65" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="65" customWidth="1"/>
-    <col min="7" max="7" width="9.5" style="64" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="4.375" style="22" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="54" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="55" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="55" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="55" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="54" customWidth="1"/>
+    <col min="8" max="8" width="15.625" style="22" customWidth="1"/>
     <col min="9" max="9" width="30.625" customWidth="1"/>
-    <col min="10" max="10" width="15.625" style="32" customWidth="1"/>
-    <col min="11" max="11" width="54.5" style="41" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="22" customWidth="1"/>
+    <col min="11" max="11" width="54.5" style="31" customWidth="1"/>
     <col min="13" max="13" width="7.75" customWidth="1"/>
     <col min="14" max="14" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="41"/>
-      <c r="K1" s="32"/>
+      <c r="B1" s="31"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="125" t="s">
         <v>314</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="143"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="133"/>
     </row>
     <row r="3" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="138"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="144"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="134"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
       <c r="K4"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="145" t="s">
+      <c r="B5" s="135" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147" t="s">
+      <c r="C5" s="136"/>
+      <c r="D5" s="137" t="s">
         <v>177</v>
       </c>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="67" t="s">
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="K5" s="68"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="148" t="s">
+      <c r="B6" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="150" t="s">
+      <c r="C6" s="140" t="s">
         <v>321</v>
       </c>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="153" t="s">
+      <c r="D6" s="141"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="143" t="s">
         <v>322</v>
       </c>
-      <c r="I6" s="154"/>
-      <c r="J6" s="152"/>
-      <c r="K6" s="155" t="s">
+      <c r="I6" s="144"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="145" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="149"/>
-      <c r="C7" s="69" t="s">
+      <c r="B7" s="139"/>
+      <c r="C7" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="60" t="s">
         <v>183</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="H7" s="71" t="s">
+      <c r="H7" s="61" t="s">
         <v>185</v>
       </c>
-      <c r="I7" s="71" t="s">
+      <c r="I7" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="J7" s="71" t="s">
+      <c r="J7" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="K7" s="156"/>
-      <c r="M7" s="72" t="s">
+      <c r="K7" s="146"/>
+      <c r="M7" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="N7" s="73" t="s">
+      <c r="N7" s="63" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="74">
+      <c r="B8" s="64">
         <v>1</v>
       </c>
-      <c r="C8" s="75" t="s">
+      <c r="C8" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="141" t="s">
+      <c r="E8" s="67"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="131" t="s">
         <v>323</v>
       </c>
-      <c r="M8" s="80">
+      <c r="M8" s="70">
         <v>0</v>
       </c>
-      <c r="N8" s="81" t="s">
+      <c r="N8" s="71" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="54">
+      <c r="B9" s="44">
         <v>2</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="72" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="84" t="s">
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="74" t="s">
         <v>193</v>
       </c>
-      <c r="I9" s="86" t="s">
+      <c r="I9" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="J9" s="87"/>
-      <c r="K9" s="142"/>
-      <c r="M9" s="80">
+      <c r="J9" s="77"/>
+      <c r="K9" s="132"/>
+      <c r="M9" s="70">
         <v>1</v>
       </c>
-      <c r="N9" s="81" t="s">
+      <c r="N9" s="71" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="54">
+      <c r="B10" s="44">
         <v>4</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="50" t="s">
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="89" t="s">
+      <c r="I10" s="79" t="s">
         <v>197</v>
       </c>
-      <c r="J10" s="90"/>
-      <c r="K10" s="91"/>
-      <c r="M10" s="80">
+      <c r="J10" s="80"/>
+      <c r="K10" s="81"/>
+      <c r="M10" s="70">
         <v>2</v>
       </c>
-      <c r="N10" s="81" t="s">
+      <c r="N10" s="71" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="54">
+      <c r="B11" s="44">
         <v>5</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="50" t="s">
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="89" t="s">
+      <c r="I11" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="90"/>
-      <c r="K11" s="91"/>
-      <c r="M11" s="80">
+      <c r="J11" s="80"/>
+      <c r="K11" s="81"/>
+      <c r="M11" s="70">
         <v>3</v>
       </c>
-      <c r="N11" s="81" t="s">
+      <c r="N11" s="71" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="33" x14ac:dyDescent="0.3">
-      <c r="B12" s="54">
+      <c r="B12" s="44">
         <v>6</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="40">
         <v>0</v>
       </c>
-      <c r="G12" s="88" t="s">
+      <c r="G12" s="78" t="s">
         <v>174</v>
       </c>
-      <c r="H12" s="90"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="90"/>
-      <c r="K12" s="93" t="s">
+      <c r="H12" s="80"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="83" t="s">
         <v>242</v>
       </c>
-      <c r="M12" s="80">
+      <c r="M12" s="70">
         <v>4</v>
       </c>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="71" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="54">
+      <c r="B13" s="44">
         <v>7</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="40">
         <v>0</v>
       </c>
-      <c r="G13" s="88" t="s">
+      <c r="G13" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="90"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="90"/>
-      <c r="K13" s="91" t="s">
+      <c r="H13" s="80"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="M13" s="80">
+      <c r="M13" s="70">
         <v>5</v>
       </c>
-      <c r="N13" s="81" t="s">
+      <c r="N13" s="71" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="54">
+      <c r="B14" s="44">
         <v>8</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="40">
         <v>0</v>
       </c>
-      <c r="G14" s="88" t="s">
+      <c r="G14" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="90"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="91" t="s">
+      <c r="H14" s="80"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="81" t="s">
         <v>204</v>
       </c>
-      <c r="M14" s="80">
+      <c r="M14" s="70">
         <v>6</v>
       </c>
-      <c r="N14" s="81" t="s">
+      <c r="N14" s="71" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="54">
+      <c r="B15" s="44">
         <v>10</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="40">
         <v>0</v>
       </c>
-      <c r="G15" s="88" t="s">
+      <c r="G15" s="78" t="s">
         <v>203</v>
       </c>
-      <c r="H15" s="90"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="91" t="s">
+      <c r="H15" s="80"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="M15" s="80">
+      <c r="M15" s="70">
         <v>7</v>
       </c>
-      <c r="N15" s="81" t="s">
+      <c r="N15" s="71" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="54">
+      <c r="B16" s="44">
         <v>11</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="50" t="s">
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="89" t="s">
+      <c r="I16" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="J16" s="90"/>
-      <c r="K16" s="91"/>
-      <c r="M16" s="80">
+      <c r="J16" s="80"/>
+      <c r="K16" s="81"/>
+      <c r="M16" s="70">
         <v>8</v>
       </c>
-      <c r="N16" s="81" t="s">
+      <c r="N16" s="71" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B17" s="54">
+      <c r="B17" s="44">
         <v>12</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="50" t="s">
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="89" t="s">
+      <c r="I17" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="57"/>
-      <c r="K17" s="95"/>
-      <c r="M17" s="96">
+      <c r="J17" s="47"/>
+      <c r="K17" s="85"/>
+      <c r="M17" s="86">
         <v>9</v>
       </c>
-      <c r="N17" s="97" t="s">
+      <c r="N17" s="87" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B18" s="54">
+      <c r="B18" s="44">
         <v>13</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="D18" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="50" t="s">
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="89" t="s">
+      <c r="I18" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="57"/>
-      <c r="K18" s="95"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="85"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B19" s="54">
+      <c r="B19" s="44">
         <v>14</v>
       </c>
-      <c r="C19" s="51" t="s">
+      <c r="C19" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="40">
         <v>0</v>
       </c>
-      <c r="G19" s="94" t="s">
+      <c r="G19" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="57"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="91" t="s">
+      <c r="H19" s="47"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="M19" s="99" t="s">
+      <c r="M19" s="89" t="s">
         <v>212</v>
       </c>
-      <c r="N19" s="100"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="101"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="90"/>
+      <c r="P19" s="91"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B20" s="54">
+      <c r="B20" s="44">
         <v>16</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="50" t="s">
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="89" t="s">
+      <c r="I20" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="57"/>
-      <c r="K20" s="95"/>
-      <c r="M20" s="102" t="s">
+      <c r="J20" s="47"/>
+      <c r="K20" s="85"/>
+      <c r="M20" s="92" t="s">
         <v>213</v>
       </c>
-      <c r="N20" s="103"/>
-      <c r="O20" s="103"/>
-      <c r="P20" s="104"/>
+      <c r="N20" s="93"/>
+      <c r="O20" s="93"/>
+      <c r="P20" s="94"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B21" s="54">
+      <c r="B21" s="44">
         <v>17</v>
       </c>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="50" t="s">
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="I21" s="89" t="s">
+      <c r="I21" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="57"/>
-      <c r="K21" s="95"/>
-      <c r="M21" s="102" t="s">
+      <c r="J21" s="47"/>
+      <c r="K21" s="85"/>
+      <c r="M21" s="92" t="s">
         <v>214</v>
       </c>
-      <c r="N21" s="103"/>
-      <c r="O21" s="103"/>
-      <c r="P21" s="104"/>
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
+      <c r="P21" s="94"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B22" s="54">
+      <c r="B22" s="44">
         <v>18</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="50" t="s">
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="I22" s="89" t="s">
+      <c r="I22" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="J22" s="57"/>
-      <c r="K22" s="95"/>
-      <c r="M22" s="102" t="s">
+      <c r="J22" s="47"/>
+      <c r="K22" s="85"/>
+      <c r="M22" s="92" t="s">
         <v>215</v>
       </c>
-      <c r="N22" s="103"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="104"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="94"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B23" s="54">
+      <c r="B23" s="44">
         <v>19</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="57" t="s">
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="I23" s="98" t="s">
+      <c r="I23" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="J23" s="57"/>
-      <c r="K23" s="95"/>
-      <c r="M23" s="102" t="s">
+      <c r="J23" s="47"/>
+      <c r="K23" s="85"/>
+      <c r="M23" s="92" t="s">
         <v>216</v>
       </c>
-      <c r="N23" s="103"/>
-      <c r="O23" s="103"/>
-      <c r="P23" s="104"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="93"/>
+      <c r="P23" s="94"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" s="54">
+      <c r="B24" s="44">
         <v>20</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="57" t="s">
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="I24" s="98" t="s">
+      <c r="I24" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="J24" s="57"/>
-      <c r="K24" s="95"/>
-      <c r="M24" s="102" t="s">
+      <c r="J24" s="47"/>
+      <c r="K24" s="85"/>
+      <c r="M24" s="92" t="s">
         <v>217</v>
       </c>
-      <c r="N24" s="103"/>
-      <c r="O24" s="103"/>
-      <c r="P24" s="104"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
+      <c r="P24" s="94"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B25" s="54">
+      <c r="B25" s="44">
         <v>21</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="50" t="s">
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="89" t="s">
+      <c r="I25" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="57"/>
-      <c r="K25" s="95"/>
-      <c r="M25" s="102" t="s">
+      <c r="J25" s="47"/>
+      <c r="K25" s="85"/>
+      <c r="M25" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="N25" s="103"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="104"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="94"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" s="54">
+      <c r="B26" s="44">
         <v>22</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="50" t="s">
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="89" t="s">
+      <c r="I26" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="J26" s="57"/>
-      <c r="K26" s="95"/>
-      <c r="M26" s="102" t="s">
+      <c r="J26" s="47"/>
+      <c r="K26" s="85"/>
+      <c r="M26" s="92" t="s">
         <v>219</v>
       </c>
-      <c r="N26" s="103"/>
-      <c r="O26" s="103"/>
-      <c r="P26" s="104"/>
+      <c r="N26" s="93"/>
+      <c r="O26" s="93"/>
+      <c r="P26" s="94"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B27" s="54">
+      <c r="B27" s="44">
         <v>23</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="50" t="s">
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="I27" s="89" t="s">
+      <c r="I27" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="J27" s="57"/>
-      <c r="K27" s="95"/>
-      <c r="M27" s="102" t="s">
+      <c r="J27" s="47"/>
+      <c r="K27" s="85"/>
+      <c r="M27" s="92" t="s">
         <v>220</v>
       </c>
-      <c r="N27" s="103"/>
-      <c r="O27" s="103"/>
-      <c r="P27" s="104"/>
+      <c r="N27" s="93"/>
+      <c r="O27" s="93"/>
+      <c r="P27" s="94"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="54">
+      <c r="B28" s="44">
         <v>24</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="50">
+      <c r="F28" s="40">
         <v>0</v>
       </c>
-      <c r="G28" s="94" t="s">
+      <c r="G28" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="50"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="95" t="s">
+      <c r="H28" s="40"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="85" t="s">
         <v>201</v>
       </c>
-      <c r="M28" s="105" t="s">
+      <c r="M28" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="N28" s="106"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="107"/>
+      <c r="N28" s="96"/>
+      <c r="O28" s="96"/>
+      <c r="P28" s="97"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B29" s="54">
+      <c r="B29" s="44">
         <v>25</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="50" t="s">
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="I29" s="89" t="s">
+      <c r="I29" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="J29" s="57"/>
-      <c r="K29" s="95"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="85"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="54">
+      <c r="B30" s="44">
         <v>26</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="50" t="s">
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="I30" s="89" t="s">
+      <c r="I30" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="J30" s="57"/>
-      <c r="K30" s="95"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="85"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="54">
+      <c r="B31" s="44">
         <v>27</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="50" t="s">
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="I31" s="89" t="s">
+      <c r="I31" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="J31" s="57"/>
-      <c r="K31" s="95"/>
+      <c r="J31" s="47"/>
+      <c r="K31" s="85"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="54">
+      <c r="B32" s="44">
         <v>28</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="50" t="s">
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="I32" s="89" t="s">
+      <c r="I32" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="J32" s="57"/>
-      <c r="K32" s="95"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="85"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="54">
+      <c r="B33" s="44">
         <v>29</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="D33" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="50" t="s">
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="I33" s="89" t="s">
+      <c r="I33" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="J33" s="57"/>
-      <c r="K33" s="95"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="85"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="54">
+      <c r="B34" s="44">
         <v>30</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="50" t="s">
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="I34" s="89" t="s">
+      <c r="I34" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="J34" s="57"/>
-      <c r="K34" s="95"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="85"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="54">
+      <c r="B35" s="44">
         <v>31</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="D35" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="94"/>
-      <c r="H35" s="50" t="s">
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="I35" s="89" t="s">
+      <c r="I35" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="J35" s="57"/>
-      <c r="K35" s="95"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="85"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B36" s="54">
+      <c r="B36" s="44">
         <v>32</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="50">
+      <c r="F36" s="40">
         <v>3</v>
       </c>
-      <c r="G36" s="94" t="s">
+      <c r="G36" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="50"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="95" t="s">
+      <c r="H36" s="40"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="85" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B37" s="54">
+      <c r="B37" s="44">
         <v>33</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="D37" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="50">
+      <c r="F37" s="40">
         <v>2</v>
       </c>
-      <c r="G37" s="94" t="s">
+      <c r="G37" s="84" t="s">
         <v>203</v>
       </c>
-      <c r="H37" s="50"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="95" t="s">
+      <c r="H37" s="40"/>
+      <c r="I37" s="79"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="85" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B38" s="54">
+      <c r="B38" s="44">
         <v>34</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="94"/>
-      <c r="H38" s="50" t="s">
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="I38" s="89" t="s">
+      <c r="I38" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="J38" s="53"/>
-      <c r="K38" s="95"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="85"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B39" s="54">
+      <c r="B39" s="44">
         <v>35</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="53" t="s">
+      <c r="D39" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="50" t="s">
+      <c r="E39" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F39" s="50">
+      <c r="F39" s="40">
         <v>2</v>
       </c>
-      <c r="G39" s="94" t="s">
+      <c r="G39" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="H39" s="50"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="95" t="s">
+      <c r="H39" s="40"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="85" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="54">
+      <c r="B40" s="44">
         <v>36</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="50" t="s">
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="I40" s="89" t="s">
+      <c r="I40" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="J40" s="53"/>
-      <c r="K40" s="95"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="85"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="54">
+      <c r="B41" s="44">
         <v>37</v>
       </c>
-      <c r="C41" s="51" t="s">
+      <c r="C41" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="D41" s="53" t="s">
+      <c r="D41" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="50" t="s">
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="I41" s="89" t="s">
+      <c r="I41" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="J41" s="53"/>
-      <c r="K41" s="95"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="85"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B42" s="54">
+      <c r="B42" s="44">
         <v>38</v>
       </c>
-      <c r="C42" s="51" t="s">
+      <c r="C42" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="D42" s="53" t="s">
+      <c r="D42" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="94"/>
-      <c r="H42" s="50" t="s">
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="I42" s="89" t="s">
+      <c r="I42" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="J42" s="53"/>
-      <c r="K42" s="95"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="85"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="54">
+      <c r="B43" s="44">
         <v>39</v>
       </c>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D43" s="53" t="s">
+      <c r="D43" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="94"/>
-      <c r="H43" s="50" t="s">
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="I43" s="89" t="s">
+      <c r="I43" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="J43" s="53"/>
-      <c r="K43" s="95"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="85"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="54">
+      <c r="B44" s="44">
         <v>40</v>
       </c>
-      <c r="C44" s="51" t="s">
+      <c r="C44" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="D44" s="53" t="s">
+      <c r="D44" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="E44" s="50" t="s">
+      <c r="E44" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="F44" s="50">
+      <c r="F44" s="40">
         <v>2</v>
       </c>
-      <c r="G44" s="94" t="s">
+      <c r="G44" s="84" t="s">
         <v>174</v>
       </c>
-      <c r="H44" s="50"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="95" t="s">
+      <c r="H44" s="40"/>
+      <c r="I44" s="79"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="85" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B45" s="54">
+      <c r="B45" s="44">
         <v>41</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="D45" s="53" t="s">
+      <c r="D45" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="E45" s="50"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="94"/>
-      <c r="H45" s="50" t="s">
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="84"/>
+      <c r="H45" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="I45" s="89" t="s">
+      <c r="I45" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="J45" s="53"/>
-      <c r="K45" s="95"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="85"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="54">
+      <c r="B46" s="44">
         <v>42</v>
       </c>
-      <c r="C46" s="51" t="s">
+      <c r="C46" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="D46" s="53" t="s">
+      <c r="D46" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="94"/>
-      <c r="H46" s="50" t="s">
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="84"/>
+      <c r="H46" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="I46" s="89" t="s">
+      <c r="I46" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="J46" s="53"/>
-      <c r="K46" s="95"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="85"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="54">
+      <c r="B47" s="44">
         <v>43</v>
       </c>
-      <c r="C47" s="51" t="s">
+      <c r="C47" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="D47" s="53" t="s">
+      <c r="D47" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="50" t="s">
+      <c r="E47" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="50">
+      <c r="F47" s="40">
         <v>4</v>
       </c>
-      <c r="G47" s="94" t="s">
+      <c r="G47" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="H47" s="50"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="95" t="s">
+      <c r="H47" s="40"/>
+      <c r="I47" s="79"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="85" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="54">
+      <c r="B48" s="44">
         <v>44</v>
       </c>
-      <c r="C48" s="51" t="s">
+      <c r="C48" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="D48" s="53" t="s">
+      <c r="D48" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="94"/>
-      <c r="H48" s="50" t="s">
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="I48" s="89" t="s">
+      <c r="I48" s="79" t="s">
         <v>138</v>
       </c>
-      <c r="J48" s="53"/>
-      <c r="K48" s="95"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="85"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49" s="54">
+      <c r="B49" s="44">
         <v>45</v>
       </c>
-      <c r="C49" s="51" t="s">
+      <c r="C49" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="D49" s="53" t="s">
+      <c r="D49" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="94"/>
-      <c r="H49" s="50" t="s">
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="I49" s="89" t="s">
+      <c r="I49" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="J49" s="53"/>
-      <c r="K49" s="95"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="85"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="54">
+      <c r="B50" s="44">
         <v>46</v>
       </c>
-      <c r="C50" s="51" t="s">
+      <c r="C50" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="D50" s="53" t="s">
+      <c r="D50" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
-      <c r="G50" s="94"/>
-      <c r="H50" s="50" t="s">
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="I50" s="89" t="s">
+      <c r="I50" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="J50" s="53"/>
-      <c r="K50" s="95"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="85"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="54">
+      <c r="B51" s="44">
         <v>47</v>
       </c>
-      <c r="C51" s="51" t="s">
+      <c r="C51" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="53" t="s">
+      <c r="D51" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
-      <c r="G51" s="94"/>
-      <c r="H51" s="50" t="s">
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="84"/>
+      <c r="H51" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="I51" s="89" t="s">
+      <c r="I51" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="J51" s="53"/>
-      <c r="K51" s="95"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="85"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B52" s="54">
+      <c r="B52" s="44">
         <v>48</v>
       </c>
-      <c r="C52" s="51" t="s">
+      <c r="C52" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="D52" s="53" t="s">
+      <c r="D52" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
-      <c r="G52" s="94"/>
-      <c r="H52" s="50" t="s">
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="84"/>
+      <c r="H52" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="I52" s="89" t="s">
+      <c r="I52" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="J52" s="53"/>
-      <c r="K52" s="95"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="85"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B53" s="54">
+      <c r="B53" s="44">
         <v>49</v>
       </c>
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="D53" s="55" t="s">
+      <c r="D53" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="E53" s="57" t="s">
+      <c r="E53" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="F53" s="57">
+      <c r="F53" s="47">
         <v>0</v>
       </c>
-      <c r="G53" s="94" t="s">
+      <c r="G53" s="84" t="s">
         <v>174</v>
       </c>
-      <c r="H53" s="57"/>
-      <c r="I53" s="98"/>
-      <c r="J53" s="55"/>
-      <c r="K53" s="95" t="s">
+      <c r="H53" s="47"/>
+      <c r="I53" s="88"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="85" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B54" s="54">
+      <c r="B54" s="44">
         <v>50</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="D54" s="55" t="s">
+      <c r="D54" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="E54" s="57" t="s">
+      <c r="E54" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="F54" s="57">
+      <c r="F54" s="47">
         <v>0</v>
       </c>
-      <c r="G54" s="94" t="s">
+      <c r="G54" s="84" t="s">
         <v>174</v>
       </c>
-      <c r="H54" s="57"/>
-      <c r="I54" s="98"/>
-      <c r="J54" s="55"/>
-      <c r="K54" s="95" t="s">
+      <c r="H54" s="47"/>
+      <c r="I54" s="88"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="85" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B55" s="54">
+      <c r="B55" s="44">
         <v>51</v>
       </c>
-      <c r="C55" s="57" t="s">
+      <c r="C55" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="D55" s="55" t="s">
+      <c r="D55" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="E55" s="57" t="s">
+      <c r="E55" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="F55" s="57">
+      <c r="F55" s="47">
         <v>0</v>
       </c>
-      <c r="G55" s="94" t="s">
+      <c r="G55" s="84" t="s">
         <v>174</v>
       </c>
-      <c r="H55" s="57"/>
-      <c r="I55" s="98"/>
-      <c r="J55" s="55"/>
-      <c r="K55" s="95" t="s">
+      <c r="H55" s="47"/>
+      <c r="I55" s="88"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="85" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="56" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="58">
+      <c r="B56" s="48">
         <v>52</v>
       </c>
-      <c r="C56" s="60" t="s">
+      <c r="C56" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="D56" s="59" t="s">
+      <c r="D56" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="E56" s="60" t="s">
+      <c r="E56" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="F56" s="60">
+      <c r="F56" s="50">
         <v>0</v>
       </c>
-      <c r="G56" s="108" t="s">
+      <c r="G56" s="98" t="s">
         <v>203</v>
       </c>
-      <c r="H56" s="60"/>
-      <c r="I56" s="109"/>
-      <c r="J56" s="59"/>
-      <c r="K56" s="110" t="s">
+      <c r="H56" s="50"/>
+      <c r="I56" s="99"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="100" t="s">
         <v>224</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="9">
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="B2:K3"/>

--- a/code_mapping/[공통] 5. 관리항목매핑정의서.xlsx
+++ b/code_mapping/[공통] 5. 관리항목매핑정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\MIG\1. GIT\공유파일\매핑정의서\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="관리항목매핑정의서" sheetId="7" r:id="rId1"/>
@@ -565,7 +565,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="326">
   <si>
     <t>SOURCE 회사코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1716,6 +1716,10 @@
   </si>
   <si>
     <t>관리항목매핑정의서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260903</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2761,92 +2765,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2997,6 +2917,90 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3579,327 +3583,327 @@
   <dimension ref="B1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.125" style="176" customWidth="1"/>
-    <col min="2" max="3" width="30.625" style="193" customWidth="1"/>
-    <col min="4" max="6" width="30.625" style="194" customWidth="1"/>
-    <col min="7" max="8" width="30.625" style="193" customWidth="1"/>
-    <col min="9" max="10" width="30.625" style="194" customWidth="1"/>
-    <col min="11" max="11" width="30.625" style="193" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="176"/>
+    <col min="1" max="1" width="2.125" style="148" customWidth="1"/>
+    <col min="2" max="3" width="30.625" style="165" customWidth="1"/>
+    <col min="4" max="6" width="30.625" style="166" customWidth="1"/>
+    <col min="7" max="8" width="30.625" style="165" customWidth="1"/>
+    <col min="9" max="10" width="30.625" style="166" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="165" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="148"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" s="55" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="164" t="s">
+      <c r="B1" s="136" t="s">
         <v>324</v>
       </c>
-      <c r="C1" s="164">
-        <v>20260513</v>
+      <c r="C1" s="136" t="s">
+        <v>325</v>
       </c>
       <c r="D1" s="54"/>
       <c r="E1" s="54"/>
       <c r="F1" s="54"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
       <c r="I1" s="54"/>
       <c r="J1" s="54"/>
-      <c r="K1" s="164"/>
+      <c r="K1" s="136"/>
     </row>
     <row r="2" spans="2:11" s="55" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
       <c r="F2" s="54"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
       <c r="I2" s="54"/>
       <c r="J2" s="54"/>
-      <c r="K2" s="164"/>
+      <c r="K2" s="136"/>
     </row>
     <row r="3" spans="2:11" s="55" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="149"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="149"/>
-      <c r="K3" s="150"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="169"/>
     </row>
     <row r="4" spans="2:11" s="55" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="151"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="153"/>
+      <c r="B4" s="170"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="172"/>
     </row>
     <row r="5" spans="2:11" s="55" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="165"/>
-      <c r="C5" s="165"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
       <c r="F5" s="54"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="165"/>
-      <c r="I5" s="167"/>
-      <c r="J5" s="167"/>
-      <c r="K5" s="165"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="137"/>
     </row>
     <row r="6" spans="2:11" s="55" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="155" t="s">
+      <c r="C6" s="127" t="s">
         <v>243</v>
       </c>
-      <c r="D6" s="156" t="s">
+      <c r="D6" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="156" t="s">
+      <c r="E6" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="156" t="s">
+      <c r="F6" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="156" t="s">
+      <c r="G6" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="156" t="s">
+      <c r="H6" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="157" t="s">
+      <c r="I6" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="157" t="s">
+      <c r="J6" s="129" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="158" t="s">
+      <c r="K6" s="130" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:11" s="55" customFormat="1" ht="116.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="159" t="s">
+      <c r="B7" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="160" t="s">
+      <c r="C7" s="132" t="s">
         <v>243</v>
       </c>
-      <c r="D7" s="160" t="s">
+      <c r="D7" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="160" t="s">
+      <c r="E7" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="161" t="s">
+      <c r="F7" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="161" t="s">
+      <c r="G7" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="162" t="s">
+      <c r="H7" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="162" t="s">
+      <c r="I7" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="162" t="s">
+      <c r="J7" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="163" t="s">
+      <c r="K7" s="135" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="168"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="170"/>
-      <c r="E8" s="170"/>
-      <c r="F8" s="171"/>
-      <c r="G8" s="172"/>
-      <c r="H8" s="173"/>
-      <c r="I8" s="174"/>
-      <c r="J8" s="174"/>
-      <c r="K8" s="175"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="142"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="145"/>
+      <c r="I8" s="146"/>
+      <c r="J8" s="146"/>
+      <c r="K8" s="147"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="177"/>
-      <c r="C9" s="178"/>
-      <c r="D9" s="179"/>
-      <c r="E9" s="179"/>
-      <c r="F9" s="180"/>
-      <c r="G9" s="181"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="183"/>
-      <c r="K9" s="184"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="150"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="154"/>
+      <c r="I9" s="155"/>
+      <c r="J9" s="155"/>
+      <c r="K9" s="156"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="177"/>
-      <c r="C10" s="178"/>
-      <c r="D10" s="179"/>
-      <c r="E10" s="179"/>
-      <c r="F10" s="180"/>
-      <c r="G10" s="181"/>
-      <c r="H10" s="182"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="183"/>
-      <c r="K10" s="184"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="150"/>
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="152"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="154"/>
+      <c r="I10" s="155"/>
+      <c r="J10" s="155"/>
+      <c r="K10" s="156"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="177"/>
-      <c r="C11" s="178"/>
-      <c r="D11" s="179"/>
-      <c r="E11" s="179"/>
-      <c r="F11" s="180"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="183"/>
-      <c r="K11" s="184"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="152"/>
+      <c r="G11" s="153"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="155"/>
+      <c r="J11" s="155"/>
+      <c r="K11" s="156"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="177"/>
-      <c r="C12" s="178"/>
-      <c r="D12" s="179"/>
-      <c r="E12" s="179"/>
-      <c r="F12" s="180"/>
-      <c r="G12" s="181"/>
-      <c r="H12" s="182"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="183"/>
-      <c r="K12" s="184"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="154"/>
+      <c r="I12" s="155"/>
+      <c r="J12" s="155"/>
+      <c r="K12" s="156"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="177"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="179"/>
-      <c r="E13" s="179"/>
-      <c r="F13" s="180"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="182"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="183"/>
-      <c r="K13" s="184"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="150"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="152"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="154"/>
+      <c r="I13" s="155"/>
+      <c r="J13" s="155"/>
+      <c r="K13" s="156"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="177"/>
-      <c r="C14" s="178"/>
-      <c r="D14" s="179"/>
-      <c r="E14" s="179"/>
-      <c r="F14" s="180"/>
-      <c r="G14" s="181"/>
-      <c r="H14" s="182"/>
-      <c r="I14" s="183"/>
-      <c r="J14" s="183"/>
-      <c r="K14" s="184"/>
+      <c r="B14" s="149"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="153"/>
+      <c r="H14" s="154"/>
+      <c r="I14" s="155"/>
+      <c r="J14" s="155"/>
+      <c r="K14" s="156"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="177"/>
-      <c r="C15" s="178"/>
-      <c r="D15" s="179"/>
-      <c r="E15" s="179"/>
-      <c r="F15" s="180"/>
-      <c r="G15" s="181"/>
-      <c r="H15" s="182"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="183"/>
-      <c r="K15" s="184"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="155"/>
+      <c r="J15" s="155"/>
+      <c r="K15" s="156"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="177"/>
-      <c r="C16" s="178"/>
-      <c r="D16" s="179"/>
-      <c r="E16" s="179"/>
-      <c r="F16" s="180"/>
-      <c r="G16" s="181"/>
-      <c r="H16" s="182"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="183"/>
-      <c r="K16" s="184"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="150"/>
+      <c r="D16" s="151"/>
+      <c r="E16" s="151"/>
+      <c r="F16" s="152"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="154"/>
+      <c r="I16" s="155"/>
+      <c r="J16" s="155"/>
+      <c r="K16" s="156"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="177"/>
-      <c r="C17" s="178"/>
-      <c r="D17" s="179"/>
-      <c r="E17" s="179"/>
-      <c r="F17" s="180"/>
-      <c r="G17" s="181"/>
-      <c r="H17" s="182"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="183"/>
-      <c r="K17" s="184"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="152"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="154"/>
+      <c r="I17" s="155"/>
+      <c r="J17" s="155"/>
+      <c r="K17" s="156"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="177"/>
-      <c r="C18" s="178"/>
-      <c r="D18" s="179"/>
-      <c r="E18" s="179"/>
-      <c r="F18" s="180"/>
-      <c r="G18" s="181"/>
-      <c r="H18" s="182"/>
-      <c r="I18" s="183"/>
-      <c r="J18" s="183"/>
-      <c r="K18" s="184"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="154"/>
+      <c r="I18" s="155"/>
+      <c r="J18" s="155"/>
+      <c r="K18" s="156"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="177"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="179"/>
-      <c r="F19" s="180"/>
-      <c r="G19" s="181"/>
-      <c r="H19" s="182"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="183"/>
-      <c r="K19" s="184"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="154"/>
+      <c r="I19" s="155"/>
+      <c r="J19" s="155"/>
+      <c r="K19" s="156"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="177"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="179"/>
-      <c r="E20" s="179"/>
-      <c r="F20" s="180"/>
-      <c r="G20" s="181"/>
-      <c r="H20" s="182"/>
-      <c r="I20" s="183"/>
-      <c r="J20" s="183"/>
-      <c r="K20" s="184"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="152"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="154"/>
+      <c r="I20" s="155"/>
+      <c r="J20" s="155"/>
+      <c r="K20" s="156"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="177"/>
-      <c r="C21" s="178"/>
-      <c r="D21" s="179"/>
-      <c r="E21" s="179"/>
-      <c r="F21" s="180"/>
-      <c r="G21" s="181"/>
-      <c r="H21" s="182"/>
-      <c r="I21" s="183"/>
-      <c r="J21" s="183"/>
-      <c r="K21" s="184"/>
+      <c r="B21" s="149"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="154"/>
+      <c r="I21" s="155"/>
+      <c r="J21" s="155"/>
+      <c r="K21" s="156"/>
     </row>
     <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="185"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="187"/>
-      <c r="E22" s="187"/>
-      <c r="F22" s="188"/>
-      <c r="G22" s="189"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="191"/>
-      <c r="J22" s="191"/>
-      <c r="K22" s="192"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="158"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="163"/>
+      <c r="J22" s="163"/>
+      <c r="K22" s="164"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ntg6Z1l9FHXRVqM7501NPHx6sZA6S3YnSNDSROvPxXpAKzNhsdoWZyekSmNNXEThVGLigVlV4Y49hu4nu8TsPA==" saltValue="jHzsU/0KH8U1SLV2YUbk4g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B3:K4"/>
   </mergeCells>
@@ -3925,30 +3929,30 @@
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="127"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="175"/>
     </row>
     <row r="3" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="130"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="177"/>
+      <c r="K3" s="178"/>
     </row>
     <row r="4" spans="2:11" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
@@ -4630,7 +4634,7 @@
       <c r="K29" s="113"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cydVYgzJrnxaNl+0m8OywAmLtkD84eUDeeghxeYqSBwxSfKP0Nlx88T2MCu1k7c2VY6xz+2+iHvQmr1RwoKzyQ==" saltValue="pvaixcPvmBYM0zNFG6zM6A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:K3"/>
   </mergeCells>
@@ -4661,30 +4665,30 @@
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="127"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="175"/>
     </row>
     <row r="3" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="130"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="177"/>
+      <c r="K3" s="178"/>
     </row>
     <row r="4" spans="2:12" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
@@ -6129,7 +6133,7 @@
       <c r="K56" s="53"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kl43ykN0BBBXNH6QLyp55FBtXgm4dsrw16n6xc/dbrKUky12/r9c5YNnXl5LxoKo2jmxxQ1okx3EQhAG6TOWMQ==" saltValue="DcVznc51bUkkQ0MU32R9NQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:K3"/>
   </mergeCells>
@@ -6178,30 +6182,30 @@
       <c r="K1" s="22"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="133"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="181"/>
     </row>
     <row r="3" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="134"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="177"/>
+      <c r="K3" s="182"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="56"/>
@@ -6216,45 +6220,45 @@
       <c r="K4"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="135" t="s">
+      <c r="B5" s="183" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137" t="s">
+      <c r="C5" s="184"/>
+      <c r="D5" s="185" t="s">
         <v>177</v>
       </c>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
       <c r="J5" s="57" t="s">
         <v>178</v>
       </c>
       <c r="K5" s="58"/>
     </row>
     <row r="6" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="186" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="140" t="s">
+      <c r="C6" s="188" t="s">
         <v>321</v>
       </c>
-      <c r="D6" s="141"/>
-      <c r="E6" s="141"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="142"/>
-      <c r="H6" s="143" t="s">
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="190"/>
+      <c r="H6" s="191" t="s">
         <v>322</v>
       </c>
-      <c r="I6" s="144"/>
-      <c r="J6" s="142"/>
-      <c r="K6" s="145" t="s">
+      <c r="I6" s="192"/>
+      <c r="J6" s="190"/>
+      <c r="K6" s="193" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="139"/>
+      <c r="B7" s="187"/>
       <c r="C7" s="59" t="s">
         <v>180</v>
       </c>
@@ -6279,7 +6283,7 @@
       <c r="J7" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="K7" s="146"/>
+      <c r="K7" s="194"/>
       <c r="M7" s="62" t="s">
         <v>187</v>
       </c>
@@ -6303,7 +6307,7 @@
       <c r="H8" s="69"/>
       <c r="I8" s="69"/>
       <c r="J8" s="69"/>
-      <c r="K8" s="131" t="s">
+      <c r="K8" s="179" t="s">
         <v>323</v>
       </c>
       <c r="M8" s="70">
@@ -6333,7 +6337,7 @@
         <v>194</v>
       </c>
       <c r="J9" s="77"/>
-      <c r="K9" s="132"/>
+      <c r="K9" s="180"/>
       <c r="M9" s="70">
         <v>1</v>
       </c>
@@ -7544,7 +7548,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Kpe/HfttNJ05YeFvvJOT3bHDLBy/vIqZPiLK/8Xv9KttEvYp1ByiU9aMQmfbMXqNCGSKHhIfON/FfdKlKKYH2w==" saltValue="8KITn5wL8tgzSVKRnmAbrA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="9">
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="B2:K3"/>
